--- a/artfynd/A 55322-2021 artfynd.xlsx
+++ b/artfynd/A 55322-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55322-2021 artfynd.xlsx
+++ b/artfynd/A 55322-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105310531</v>
+        <v>105314294</v>
       </c>
       <c r="B2" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575107.7195112016</v>
+        <v>575109</v>
       </c>
       <c r="R2" t="n">
-        <v>6842266.113114777</v>
+        <v>6842247</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105310790</v>
+        <v>105314296</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575115.278801291</v>
+        <v>575106</v>
       </c>
       <c r="R3" t="n">
-        <v>6842246.350533606</v>
+        <v>6842259</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +845,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105310781</v>
+        <v>105314298</v>
       </c>
       <c r="B4" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575085.6973427543</v>
+        <v>575108</v>
       </c>
       <c r="R4" t="n">
-        <v>6842425.998148779</v>
+        <v>6842274</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,19 +947,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105310532</v>
+        <v>105890745</v>
       </c>
       <c r="B5" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575014.8035120002</v>
+        <v>575115</v>
       </c>
       <c r="R5" t="n">
-        <v>6842256.019783405</v>
+        <v>6842239</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,21 +1049,11 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1122,11 +1062,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Ca 20 dm2</t>
-        </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -1148,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105310796</v>
+        <v>105890746</v>
       </c>
       <c r="B6" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574962.290103982</v>
+        <v>575146</v>
       </c>
       <c r="R6" t="n">
-        <v>6842223.560129189</v>
+        <v>6842251</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,19 +1151,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105310779</v>
+        <v>105310528</v>
       </c>
       <c r="B7" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>2387</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575083.9181571385</v>
+        <v>575079</v>
       </c>
       <c r="R7" t="n">
-        <v>6842485.738733225</v>
+        <v>6842431</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,21 +1253,11 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1361,11 +1266,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>På gammal gran i annars yngre del.</t>
-        </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -1387,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105314291</v>
+        <v>105310525</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575125.7057772344</v>
+        <v>575116</v>
       </c>
       <c r="R8" t="n">
-        <v>6842269.35265654</v>
+        <v>6842473</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1460,19 +1355,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105314295</v>
+        <v>105310526</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1544,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575118.6228352846</v>
+        <v>575077</v>
       </c>
       <c r="R9" t="n">
-        <v>6842267.300119412</v>
+        <v>6842473</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1577,19 +1457,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,62 +1491,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105310096</v>
+        <v>105310527</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575051</v>
+        <v>575032</v>
       </c>
       <c r="R10" t="n">
-        <v>6842290</v>
+        <v>6842444</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1717,14 +1570,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Ca 200 plantor</t>
-        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -1746,15 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105310791</v>
+        <v>105310529</v>
       </c>
       <c r="B11" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575111.1180551117</v>
+        <v>575093</v>
       </c>
       <c r="R11" t="n">
-        <v>6842241.040524011</v>
+        <v>6842411</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,21 +1661,11 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1842,11 +1674,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Rikligt på granar i denna del</t>
-        </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -1868,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105310786</v>
+        <v>105310530</v>
       </c>
       <c r="B12" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575128.2211510839</v>
+        <v>575214</v>
       </c>
       <c r="R12" t="n">
-        <v>6842328.240842265</v>
+        <v>6842312</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1941,21 +1763,11 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1964,11 +1776,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe. Även korallblylav på samma.</t>
-        </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -1990,37 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105310783</v>
+        <v>105310531</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2030,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575091.0562150652</v>
+        <v>575108</v>
       </c>
       <c r="R13" t="n">
-        <v>6842419.947350182</v>
+        <v>6842266</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,19 +1865,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,62 +1899,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105310099</v>
+        <v>105310532</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575002</v>
+        <v>575015</v>
       </c>
       <c r="R14" t="n">
-        <v>6842246</v>
+        <v>6842256</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2203,13 +1978,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>200 plantor ca</t>
+          <t>Ca 20 dm2</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2232,15 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105310793</v>
+        <v>105314287</v>
       </c>
       <c r="B15" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2272,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575112.7797383786</v>
+        <v>575090</v>
       </c>
       <c r="R15" t="n">
-        <v>6842251.989587895</v>
+        <v>6842428</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2305,19 +2074,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,15 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105314300</v>
+        <v>105314288</v>
       </c>
       <c r="B16" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575078.6527607094</v>
+        <v>575098</v>
       </c>
       <c r="R16" t="n">
-        <v>6842291.574144249</v>
+        <v>6842311</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2422,19 +2176,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2466,15 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105310782</v>
+        <v>105314290</v>
       </c>
       <c r="B17" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2506,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575078.7078573353</v>
+        <v>575129</v>
       </c>
       <c r="R17" t="n">
-        <v>6842419.677811543</v>
+        <v>6842250</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2539,19 +2278,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2583,15 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105310789</v>
+        <v>105314297</v>
       </c>
       <c r="B18" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2623,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575145.1391743333</v>
+        <v>575100</v>
       </c>
       <c r="R18" t="n">
-        <v>6842249.849486266</v>
+        <v>6842273</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2656,21 +2380,11 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2679,6 +2393,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -2700,15 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105314288</v>
+        <v>105314300</v>
       </c>
       <c r="B19" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2740,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575098.1867320681</v>
+        <v>575079</v>
       </c>
       <c r="R19" t="n">
-        <v>6842310.97897503</v>
+        <v>6842292</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2773,19 +2487,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2817,62 +2521,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105310098</v>
+        <v>105314286</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574998</v>
+        <v>575091</v>
       </c>
       <c r="R20" t="n">
-        <v>6842258</v>
+        <v>6842506</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2913,14 +2600,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>300 plantor ca</t>
-        </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -2942,15 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105314287</v>
+        <v>105314291</v>
       </c>
       <c r="B21" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2958,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2982,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575089.9303589389</v>
+        <v>575126</v>
       </c>
       <c r="R21" t="n">
-        <v>6842427.9883258</v>
+        <v>6842269</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3015,19 +2691,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3059,15 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105310528</v>
+        <v>105314292</v>
       </c>
       <c r="B22" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3075,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2387</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3099,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575078.9447349537</v>
+        <v>575123</v>
       </c>
       <c r="R22" t="n">
-        <v>6842430.595194306</v>
+        <v>6842249</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3132,19 +2793,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3176,62 +2827,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105310093</v>
+        <v>105314295</v>
       </c>
       <c r="B23" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575063</v>
+        <v>575119</v>
       </c>
       <c r="R23" t="n">
-        <v>6842307</v>
+        <v>6842267</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3272,14 +2906,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>200 plantor ca</t>
-        </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -3301,15 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105316100</v>
+        <v>105314299</v>
       </c>
       <c r="B24" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3317,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3341,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574975.2278217981</v>
+        <v>575119</v>
       </c>
       <c r="R24" t="n">
-        <v>6842218.622890346</v>
+        <v>6842291</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3374,19 +2997,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3418,15 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105310092</v>
+        <v>105310780</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,46 +3042,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575118</v>
+        <v>575071</v>
       </c>
       <c r="R25" t="n">
-        <v>6842296</v>
+        <v>6842430</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3514,14 +3110,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Ca 200 plantor</t>
-        </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -3543,37 +3133,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105314298</v>
+        <v>105310783</v>
       </c>
       <c r="B26" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3583,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575108.4934036754</v>
+        <v>575091</v>
       </c>
       <c r="R26" t="n">
-        <v>6842274.195925248</v>
+        <v>6842420</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3616,19 +3201,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3660,37 +3235,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105310784</v>
+        <v>105310787</v>
       </c>
       <c r="B27" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3700,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575051.971543372</v>
+        <v>575146</v>
       </c>
       <c r="R27" t="n">
-        <v>6842316.61279671</v>
+        <v>6842319</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3733,21 +3303,11 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3756,11 +3316,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>På rönn</t>
-        </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -3782,37 +3337,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105310091</v>
+        <v>105310788</v>
       </c>
       <c r="B28" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3822,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575227.6453446136</v>
+        <v>575223</v>
       </c>
       <c r="R28" t="n">
-        <v>6842279.646292841</v>
+        <v>6842308</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3855,19 +3405,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3899,37 +3439,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>105310785</v>
+        <v>105310790</v>
       </c>
       <c r="B29" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3939,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575123.2141903781</v>
+        <v>575115</v>
       </c>
       <c r="R29" t="n">
-        <v>6842318.167870039</v>
+        <v>6842246</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3972,19 +3507,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4016,37 +3541,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>105314290</v>
+        <v>105310795</v>
       </c>
       <c r="B30" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4056,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575128.9698073862</v>
+        <v>575029</v>
       </c>
       <c r="R30" t="n">
-        <v>6842250.445257219</v>
+        <v>6842267</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4089,19 +3609,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4133,15 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>105310787</v>
+        <v>105310778</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4149,21 +3654,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4173,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575146.0118325895</v>
+        <v>575106</v>
       </c>
       <c r="R31" t="n">
-        <v>6842318.665805176</v>
+        <v>6842423</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4206,19 +3711,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4250,19 +3745,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>105310792</v>
+        <v>105310779</v>
       </c>
       <c r="B32" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4290,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575109.042184345</v>
+        <v>575084</v>
       </c>
       <c r="R32" t="n">
-        <v>6842249.061172487</v>
+        <v>6842486</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4323,21 +3813,11 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4346,6 +3826,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>På gammal gran i annars yngre del.</t>
+        </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -4367,62 +3852,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>105310094</v>
+        <v>105310782</v>
       </c>
       <c r="B33" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575065</v>
+        <v>575079</v>
       </c>
       <c r="R33" t="n">
-        <v>6842288</v>
+        <v>6842420</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4463,14 +3931,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>20 plantor</t>
-        </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -4492,37 +3954,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>105314292</v>
+        <v>105310789</v>
       </c>
       <c r="B34" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4532,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575122.8160364807</v>
+        <v>575145</v>
       </c>
       <c r="R34" t="n">
-        <v>6842249.361931731</v>
+        <v>6842250</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4565,19 +4022,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4609,37 +4056,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105310525</v>
+        <v>105310791</v>
       </c>
       <c r="B35" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2809</v>
+        <v>6426</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4649,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575116.028267629</v>
+        <v>575111</v>
       </c>
       <c r="R35" t="n">
-        <v>6842473.155557856</v>
+        <v>6842241</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4682,21 +4124,11 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4705,6 +4137,11 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Rikligt på granar i denna del</t>
+        </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
@@ -4726,62 +4163,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>105310097</v>
+        <v>105310792</v>
       </c>
       <c r="B36" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575029</v>
+        <v>575109</v>
       </c>
       <c r="R36" t="n">
-        <v>6842274</v>
+        <v>6842249</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4822,14 +4242,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>200 plantor</t>
-        </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
@@ -4851,19 +4265,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>105310794</v>
+        <v>105310793</v>
       </c>
       <c r="B37" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4891,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575105.8196788827</v>
+        <v>575113</v>
       </c>
       <c r="R37" t="n">
-        <v>6842266.071635744</v>
+        <v>6842252</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4924,19 +4333,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4968,62 +4367,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105310095</v>
+        <v>105310794</v>
       </c>
       <c r="B38" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575059</v>
+        <v>575106</v>
       </c>
       <c r="R38" t="n">
-        <v>6842305</v>
+        <v>6842266</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5064,14 +4446,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>10 plantor</t>
-        </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
@@ -5093,62 +4469,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>105310090</v>
+        <v>105310796</v>
       </c>
       <c r="B39" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575234</v>
+        <v>574962</v>
       </c>
       <c r="R39" t="n">
-        <v>6842301</v>
+        <v>6842224</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5189,14 +4548,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>100 plantor ca</t>
-        </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
@@ -5218,15 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>105310529</v>
+        <v>105310786</v>
       </c>
       <c r="B40" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5234,21 +4582,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2809</v>
+        <v>6439</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5258,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575093.1526564577</v>
+        <v>575128</v>
       </c>
       <c r="R40" t="n">
-        <v>6842410.978651907</v>
+        <v>6842328</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5291,21 +4639,11 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5314,6 +4652,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe. Även korallblylav på samma.</t>
+        </is>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
@@ -5335,37 +4678,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>105310526</v>
+        <v>105310781</v>
       </c>
       <c r="B41" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5375,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575077.0736952362</v>
+        <v>575086</v>
       </c>
       <c r="R41" t="n">
-        <v>6842472.779550085</v>
+        <v>6842426</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5408,19 +4746,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5452,15 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>105310530</v>
+        <v>105316100</v>
       </c>
       <c r="B42" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5468,21 +4791,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5492,10 +4815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575214.1164348521</v>
+        <v>574975</v>
       </c>
       <c r="R42" t="n">
-        <v>6842311.613934093</v>
+        <v>6842219</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5525,19 +4848,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5569,15 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>105310780</v>
+        <v>105310088</v>
       </c>
       <c r="B43" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5585,21 +4893,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220075</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5609,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575070.870833997</v>
+        <v>575059</v>
       </c>
       <c r="R43" t="n">
-        <v>6842430.418980757</v>
+        <v>6842463</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5642,19 +4950,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5686,50 +4984,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>105310795</v>
+        <v>105310087</v>
       </c>
       <c r="B44" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104803</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>With.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575028.8143962862</v>
+        <v>575120</v>
       </c>
       <c r="R44" t="n">
-        <v>6842267.23805661</v>
+        <v>6842490</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5759,29 +5056,25 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Lite osäker</t>
+        </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
@@ -5803,50 +5096,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>105314299</v>
+        <v>105310090</v>
       </c>
       <c r="B45" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575118.5696496681</v>
+        <v>575234</v>
       </c>
       <c r="R45" t="n">
-        <v>6842291.496638211</v>
+        <v>6842301</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5876,29 +5176,25 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>100 plantor ca</t>
+        </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
@@ -5920,50 +5216,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>105314294</v>
+        <v>105310092</v>
       </c>
       <c r="B46" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575109.0836018689</v>
+        <v>575118</v>
       </c>
       <c r="R46" t="n">
-        <v>6842247.164202581</v>
+        <v>6842296</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5993,29 +5296,25 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Ca 200 plantor</t>
+        </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
@@ -6037,50 +5336,57 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>105314286</v>
+        <v>105310093</v>
       </c>
       <c r="B47" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575091.0822103978</v>
+        <v>575063</v>
       </c>
       <c r="R47" t="n">
-        <v>6842505.821363471</v>
+        <v>6842307</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6110,29 +5416,25 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>200 plantor ca</t>
+        </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
@@ -6154,50 +5456,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>105314297</v>
+        <v>105310094</v>
       </c>
       <c r="B48" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575099.9648844845</v>
+        <v>575065</v>
       </c>
       <c r="R48" t="n">
-        <v>6842273.060797861</v>
+        <v>6842288</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6227,33 +5536,24 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>20 plantor</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -6276,50 +5576,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>105310527</v>
+        <v>105310095</v>
       </c>
       <c r="B49" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575031.6054705232</v>
+        <v>575059</v>
       </c>
       <c r="R49" t="n">
-        <v>6842444.269985935</v>
+        <v>6842305</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6349,29 +5656,25 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>10 plantor</t>
+        </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
@@ -6393,50 +5696,57 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>105310778</v>
+        <v>105310096</v>
       </c>
       <c r="B50" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575105.7171316126</v>
+        <v>575051</v>
       </c>
       <c r="R50" t="n">
-        <v>6842423.114092813</v>
+        <v>6842290</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6466,29 +5776,25 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Ca 200 plantor</t>
+        </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
@@ -6510,50 +5816,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>105310788</v>
+        <v>105310097</v>
       </c>
       <c r="B51" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575223.233852067</v>
+        <v>575029</v>
       </c>
       <c r="R51" t="n">
-        <v>6842307.543146697</v>
+        <v>6842274</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6583,29 +5896,25 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>200 plantor</t>
+        </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
@@ -6627,50 +5936,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>105314296</v>
+        <v>105310098</v>
       </c>
       <c r="B52" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575105.9749882424</v>
+        <v>574998</v>
       </c>
       <c r="R52" t="n">
-        <v>6842258.958028337</v>
+        <v>6842258</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6700,29 +6016,25 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>300 plantor ca</t>
+        </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
@@ -6744,50 +6056,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>105890746</v>
+        <v>105310099</v>
       </c>
       <c r="B53" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575146.0683760708</v>
+        <v>575002</v>
       </c>
       <c r="R53" t="n">
-        <v>6842250.818720882</v>
+        <v>6842246</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6817,29 +6136,25 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>200 plantor ca</t>
+        </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
@@ -6861,37 +6176,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>105890745</v>
+        <v>105310091</v>
       </c>
       <c r="B54" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6901,10 +6211,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575114.9591681552</v>
+        <v>575228</v>
       </c>
       <c r="R54" t="n">
-        <v>6842239.226514517</v>
+        <v>6842280</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6934,19 +6244,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6978,15 +6278,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>105310087</v>
+        <v>105310784</v>
       </c>
       <c r="B55" t="n">
-        <v>101854</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6994,38 +6289,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220461</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>With.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Selanbacken, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575119.9298130695</v>
+        <v>575052</v>
       </c>
       <c r="R55" t="n">
-        <v>6842490.320474718</v>
+        <v>6842317</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7055,34 +6346,23 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Lite osäker</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -7102,6 +6382,108 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>105310785</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Selanbacken, Hls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>575123</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6842318</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55322-2021 artfynd.xlsx
+++ b/artfynd/A 55322-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314294</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314296</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314298</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105890745</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105890746</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310528</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310525</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310526</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310527</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310529</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310530</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310531</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2003,6 +2068,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310532</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2105,6 +2175,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314287</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314288</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2309,6 +2389,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314290</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2416,6 +2501,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314297</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2518,6 +2608,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314300</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314286</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2722,6 +2822,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314291</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2824,6 +2929,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314292</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2926,6 +3036,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314295</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3028,6 +3143,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314299</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3130,6 +3250,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310780</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3232,6 +3357,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310783</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3334,6 +3464,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310787</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3436,6 +3571,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310788</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3538,6 +3678,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310790</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3640,6 +3785,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310795</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3742,6 +3892,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310778</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3849,6 +4004,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310779</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3951,6 +4111,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310782</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4053,6 +4218,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310789</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4160,6 +4330,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310791</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4262,6 +4437,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310792</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4364,6 +4544,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310793</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4466,6 +4651,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310794</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4568,6 +4758,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310796</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4675,6 +4870,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310786</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4777,6 +4977,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310781</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4879,6 +5084,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105316100</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4981,6 +5191,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310088</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5093,6 +5308,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310087</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5213,6 +5433,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310090</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5333,6 +5558,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310092</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5453,6 +5683,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310093</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5573,6 +5808,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310094</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5693,6 +5933,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310095</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5813,6 +6058,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310096</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5933,6 +6183,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310097</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6053,6 +6308,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310098</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6173,6 +6433,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310099</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6275,6 +6540,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310091</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6382,6 +6652,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310784</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6484,8 +6759,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310785</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>